--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830C928C-BEC6-4B5C-8280-C0683B9E8659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37553CD-0339-41AB-9BE0-394614F41247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20760" yWindow="-1740" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -98,6 +98,13 @@
   </si>
   <si>
     <t>ActiveMatch: End-to-end Semi-supervised Active Representation Learning</t>
+  </si>
+  <si>
+    <t>DeepAL: Deep Active Learning in Python</t>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -140,8 +147,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -422,8 +432,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:C23"/>
+  <dimension ref="B1:C25"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="2" max="2" width="8.6640625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="3:3">
       <c r="C1" t="s">
@@ -505,39 +518,52 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="2:3">
       <c r="C17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="2:3">
       <c r="C18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="3:3">
+    <row r="19" spans="2:3">
       <c r="C19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="3:3">
+    <row r="20" spans="2:3">
       <c r="C20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:3">
+    <row r="21" spans="2:3">
       <c r="C21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="3:3">
+    <row r="22" spans="2:3">
       <c r="C22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="3:3">
+    <row r="23" spans="2:3">
       <c r="C23" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37553CD-0339-41AB-9BE0-394614F41247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD3BF04-E636-4577-A285-E8C8E0412C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16260" yWindow="-2820" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -105,6 +105,9 @@
   <si>
     <t>×</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Deep Active Learning for Anomaly Detection</t>
   </si>
 </sst>
 </file>
@@ -432,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C25"/>
+  <dimension ref="B1:C26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -566,6 +569,11 @@
         <v>23</v>
       </c>
     </row>
+    <row r="26" spans="2:3">
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD3BF04-E636-4577-A285-E8C8E0412C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212489B7-A59D-4538-BDE3-15F33CF408A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16260" yWindow="-2820" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20286" yWindow="-1734" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Deep Active Learning for Anomaly Detection</t>
+  </si>
+  <si>
+    <t>Active Learning for Convolutional Neural Networks: A Core-Set Approach</t>
   </si>
 </sst>
 </file>
@@ -435,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C26"/>
+  <dimension ref="B1:C27"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -574,6 +577,11 @@
         <v>25</v>
       </c>
     </row>
+    <row r="27" spans="2:3">
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212489B7-A59D-4538-BDE3-15F33CF408A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842B344-5CB8-498B-9269-7F05FF0E6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20286" yWindow="-1734" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Active Learning for Convolutional Neural Networks: A Core-Set Approach</t>
+  </si>
+  <si>
+    <t>Pre-training without Natural Images</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C27"/>
+  <dimension ref="B1:C28"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -582,6 +585,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="28" spans="2:3">
+      <c r="C28" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6842B344-5CB8-498B-9269-7F05FF0E6B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79D9469-2EBD-4243-9BD6-7A5C1CED314F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20286" yWindow="-1734" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -114,6 +114,13 @@
   </si>
   <si>
     <t>Pre-training without Natural Images</t>
+  </si>
+  <si>
+    <t>Can Vision Transformers Learn without Natural Images?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Formula-driven Supervised Learning with Recursive Tiling Patterns</t>
   </si>
 </sst>
 </file>
@@ -441,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C28"/>
+  <dimension ref="B1:C30"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -590,6 +597,16 @@
         <v>27</v>
       </c>
     </row>
+    <row r="29" spans="2:3">
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79D9469-2EBD-4243-9BD6-7A5C1CED314F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769945E2-0BDE-40BE-8779-C2DB4EF47487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20286" yWindow="-1734" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15858" yWindow="-2124" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -121,6 +121,10 @@
   </si>
   <si>
     <t>Formula-driven Supervised Learning with Recursive Tiling Patterns</t>
+  </si>
+  <si>
+    <t>ACCV</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -448,162 +452,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:3">
-      <c r="C1" t="s">
+    <row r="1" spans="4:4">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="3:3">
-      <c r="C2" t="s">
+    <row r="2" spans="4:4">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
+    <row r="3" spans="4:4">
+      <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="3:3">
-      <c r="C4" t="s">
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:3">
-      <c r="C5" t="s">
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
-      <c r="C6" t="s">
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
-      <c r="C7" t="s">
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:3">
-      <c r="C8" t="s">
+    <row r="8" spans="4:4">
+      <c r="D8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="3:3">
-      <c r="C9" t="s">
+    <row r="9" spans="4:4">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="3:3">
-      <c r="C10" t="s">
+    <row r="10" spans="4:4">
+      <c r="D10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="3:3">
-      <c r="C11" t="s">
+    <row r="11" spans="4:4">
+      <c r="D11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="3:3">
-      <c r="C12" t="s">
+    <row r="12" spans="4:4">
+      <c r="D12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:3">
-      <c r="C13" t="s">
+    <row r="13" spans="4:4">
+      <c r="D13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="3:3">
-      <c r="C14" t="s">
+    <row r="14" spans="4:4">
+      <c r="D14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="3:3">
-      <c r="C15" t="s">
+    <row r="15" spans="4:4">
+      <c r="D15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="3:3">
-      <c r="C16" t="s">
+    <row r="16" spans="4:4">
+      <c r="D16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:3">
-      <c r="C17" t="s">
+    <row r="17" spans="1:4">
+      <c r="D17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
-      <c r="C18" t="s">
+    <row r="18" spans="1:4">
+      <c r="D18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
-      <c r="C19" t="s">
+    <row r="19" spans="1:4">
+      <c r="D19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
-      <c r="C20" t="s">
+    <row r="20" spans="1:4">
+      <c r="D20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="C21" t="s">
+    <row r="21" spans="1:4">
+      <c r="D21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="C22" t="s">
+    <row r="22" spans="1:4">
+      <c r="D22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
-      <c r="C23" t="s">
+    <row r="23" spans="1:4">
+      <c r="D23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
-      <c r="C24" t="s">
+    <row r="24" spans="1:4">
+      <c r="D24" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
-      <c r="B25" s="1" t="s">
+    <row r="25" spans="1:4">
+      <c r="C25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="C26" t="s">
+    <row r="26" spans="1:4">
+      <c r="D26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
-      <c r="C27" t="s">
+    <row r="27" spans="1:4">
+      <c r="D27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
-      <c r="C28" t="s">
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
-      <c r="C29" t="s">
+    <row r="29" spans="1:4">
+      <c r="D29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
-      <c r="C30" t="s">
+    <row r="30" spans="1:4">
+      <c r="D30" t="s">
         <v>29</v>
       </c>
     </row>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769945E2-0BDE-40BE-8779-C2DB4EF47487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07047B91-F45E-45FA-BA8C-49A454C72108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15858" yWindow="-2124" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -124,6 +124,13 @@
   </si>
   <si>
     <t>ACCV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Agreement-Discrepancy-Selection Active Learning with Progressive Distribution Alignment</t>
+  </si>
+  <si>
+    <t>AAAI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -452,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -617,6 +624,17 @@
         <v>29</v>
       </c>
     </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07047B91-F45E-45FA-BA8C-49A454C72108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A5E9AF-92BB-4804-B57F-1154830C4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -131,6 +131,13 @@
   </si>
   <si>
     <t>AAAI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>How Much More Data Do I Need? Estimating Requirements for Downstream Tasks</t>
+  </si>
+  <si>
+    <t>CVPR</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -459,88 +466,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:4">
+    <row r="1" spans="1:4">
       <c r="D1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="4:4">
+    <row r="2" spans="1:4">
       <c r="D2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="4:4">
+    <row r="3" spans="1:4">
       <c r="D3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="4:4">
+    <row r="4" spans="1:4">
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="4:4">
+    <row r="5" spans="1:4">
       <c r="D5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="4:4">
+    <row r="6" spans="1:4">
       <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="4:4">
+    <row r="7" spans="1:4">
       <c r="D7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="4:4">
+    <row r="8" spans="1:4">
       <c r="D8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="4:4">
+    <row r="9" spans="1:4">
       <c r="D9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="4:4">
+    <row r="10" spans="1:4">
       <c r="D10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="4:4">
+    <row r="11" spans="1:4">
       <c r="D11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="4:4">
+    <row r="12" spans="1:4">
       <c r="D12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="4:4">
+    <row r="13" spans="1:4">
       <c r="D13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="4:4">
+    <row r="14" spans="1:4">
       <c r="D14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="4:4">
+    <row r="15" spans="1:4">
       <c r="D15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="4:4">
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2022</v>
+      </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
@@ -633,6 +646,17 @@
       </c>
       <c r="D31" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A5E9AF-92BB-4804-B57F-1154830C4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0B3B69-D6A7-4D98-B778-031BE54304D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7482" yWindow="-2472" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -138,6 +138,24 @@
   </si>
   <si>
     <t>CVPR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Learning Curves for Analysis of Deep Networks</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Exploiting Diversity of Unlabeled Data for Label-Efficient Semi-Supervised Active Learning</t>
+  </si>
+  <si>
+    <t>ICPR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ICCV</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -466,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -628,11 +646,23 @@
       </c>
     </row>
     <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2022</v>
+      </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2022</v>
+      </c>
       <c r="D30" t="s">
         <v>29</v>
       </c>
@@ -657,6 +687,28 @@
       </c>
       <c r="D32" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D34" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0B3B69-D6A7-4D98-B778-031BE54304D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E119D99-9F23-42FA-99AB-370FE34EC338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7482" yWindow="-2472" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>A Comparative Survey of Deep Active Learnin</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Deep Reinforcement Active Learning for Human-In-The-Loop Person Re-Identification</t>
   </si>
   <si>
@@ -156,6 +152,10 @@
   </si>
   <si>
     <t>ICCV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A Comparative Survey of Deep Active Learning</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -502,213 +502,213 @@
     </row>
     <row r="3" spans="1:4">
       <c r="D3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="D4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="D5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="D6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="D9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="D10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="D11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="D12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="D13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="D15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1">
         <v>2022</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="D17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="D18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="D19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="D20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="D21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="D22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="D23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="D24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="C25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="D26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="D27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" s="1">
         <v>2020</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1">
         <v>2022</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1">
         <v>2022</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1">
         <v>2021</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="1">
         <v>2022</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="1">
         <v>2020</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="1">
         <v>2022</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E119D99-9F23-42FA-99AB-370FE34EC338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937EE8A9-0509-4D70-ACD6-8FC900102AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40290" yWindow="-6438" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -157,6 +157,106 @@
   <si>
     <t>A Comparative Survey of Deep Active Learning</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Information Gain Sampling for Active Learning in Medical Image Classification</t>
+  </si>
+  <si>
+    <t>MICCAI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patient Aware Active Learning for Fine-Grained OCT Classification</t>
+  </si>
+  <si>
+    <t>ICIP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Using Self-Supervised Pretext Tasks for Active Learning</t>
+  </si>
+  <si>
+    <t>ECCV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Boosting Active Learning via Improving Test Performance</t>
+  </si>
+  <si>
+    <t>Stopping Criterion for Active Learning Based on Error Stability</t>
+  </si>
+  <si>
+    <t>In Defense of Core-set: A Density-aware Core-set Selection for Active Learning</t>
+  </si>
+  <si>
+    <t>KDD</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The Vendi Score: A Diversity Evaluation Metric for Machine Learning</t>
+  </si>
+  <si>
+    <t>Consistency-based Semi-supervised Active Learning: Towards Minimizing Labeling Cost</t>
+  </si>
+  <si>
+    <t>TiDAL: Learning Training Dynamics for Active Learning</t>
+  </si>
+  <si>
+    <t>Deep Active Ensemble Sampling For Image Classification</t>
+  </si>
+  <si>
+    <t>Making Your First Choice: To Address Cold Start Problem in Vision Active</t>
+  </si>
+  <si>
+    <t>Active Learning on a Budget: Opposite Strategies Suit High and Low Budgets</t>
+  </si>
+  <si>
+    <t>ICML</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Optimizing Data Collection for Machine Learning</t>
+  </si>
+  <si>
+    <t>NIPS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Responsible Active Learning via Human-in-the-loop Peer Study</t>
+  </si>
+  <si>
+    <t>TMLR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>How Much a Model Be Trained by Passive Learning Before Active Learning</t>
+  </si>
+  <si>
+    <t>IEEE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bootstrap your own latent: A new approach to self-supervised Learning</t>
+  </si>
+  <si>
+    <t>Barlow Twins: Self-Supervised Learning via Redundancy Reduction</t>
+  </si>
+  <si>
+    <t>Deep Active Learning Using Barlow Twins</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Self-Supervised Learning with Swin Transformers</t>
+  </si>
+  <si>
+    <t>MoBYv2AL: Self-supervised Active Learning for Image Classification</t>
+  </si>
+  <si>
+    <t>BMVC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Self-Paced Active Learning: Query the Right Thing at the Right Time</t>
   </si>
 </sst>
 </file>
@@ -484,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -711,6 +811,237 @@
         <v>36</v>
       </c>
     </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D47" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D54" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937EE8A9-0509-4D70-ACD6-8FC900102AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C262C8B-11F5-46C8-9511-8D18FF1074BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-40290" yWindow="-6438" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10820" yWindow="2820" windowWidth="14400" windowHeight="8110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -257,6 +257,16 @@
   </si>
   <si>
     <t>Self-Paced Active Learning: Query the Right Thing at the Right Time</t>
+  </si>
+  <si>
+    <t>Towards Semi-Supervised Deep Facial Expression Recognition with An Adaptive Confidence Margin</t>
+  </si>
+  <si>
+    <t>FixMatch: Simplifying Semi-Supervised Learning with Consistency and Confidence</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Forgetful Active Learning with Switch Events: Efficient Sampling for Out-of-Distribution Data</t>
   </si>
 </sst>
 </file>
@@ -584,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -1042,6 +1052,39 @@
         <v>69</v>
       </c>
     </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D56" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D58" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C262C8B-11F5-46C8-9511-8D18FF1074BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B39614-56B0-4B72-A6C1-D1A90488503C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="2820" windowWidth="14400" windowHeight="8110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="88">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -267,6 +267,53 @@
   </si>
   <si>
     <t>Forgetful Active Learning with Switch Events: Efficient Sampling for Out-of-Distribution Data</t>
+  </si>
+  <si>
+    <t>Improving greedy core-set configurations for active learning with uncertainty-scaled distances</t>
+  </si>
+  <si>
+    <t>BatchBALD: Efficient and Diverse Batch Acquisition for Deep Bayesian Active Learning</t>
+  </si>
+  <si>
+    <t>Reducing Label Effort: Self-Supervised meets Active Learning</t>
+  </si>
+  <si>
+    <t>ICCVW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Momentum Contrast for Unsupervised Visual Representation Learning</t>
+  </si>
+  <si>
+    <t>Improved Baselines with Momentum Contrastive Learning</t>
+  </si>
+  <si>
+    <t>An Empirical Study of Training Self-Supervised Vision Transformers</t>
+  </si>
+  <si>
+    <t>Emerging Properties in Self-Supervised Vision Transformers</t>
+  </si>
+  <si>
+    <t>Big Self-Supervised Models are Strong Semi-Supervised Learners</t>
+  </si>
+  <si>
+    <t>CoMatch: Semi-supervised Learning with Contrastive Graph Regularization</t>
+  </si>
+  <si>
+    <t>Class-Aware Contrastive Semi-Supervised Learning</t>
+  </si>
+  <si>
+    <t>FlexMatch: Boosting Semi-Supervised Learning with Curriculum Pseudo Labeling</t>
+  </si>
+  <si>
+    <t>FreeMatch: Self-adaptive Thresholding for Semi-supervised Learning</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Broken Neural Scaling Laws</t>
   </si>
 </sst>
 </file>
@@ -594,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="8.6640625" style="1"/>
@@ -1085,6 +1132,149 @@
         <v>72</v>
       </c>
     </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D64" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2020</v>
+      </c>
+      <c r="D66" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D67" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D69" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D70" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D71" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B39614-56B0-4B72-A6C1-D1A90488503C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AF081C-5312-46B4-B42B-504B2AF62205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-3960" windowWidth="23232" windowHeight="12552" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11520" yWindow="-3864" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="91">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -314,6 +314,16 @@
   </si>
   <si>
     <t>Broken Neural Scaling Laws</t>
+  </si>
+  <si>
+    <t>Beyond neural scaling laws: beating power law scaling via data pruning</t>
+  </si>
+  <si>
+    <t>Active Deep Learning Guided by Efficient Gaussian Process Surrogates</t>
+  </si>
+  <si>
+    <t>Towards active learning: A stopping criterion for the sequential sampling of grain boundary degrees of freedom</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -641,10 +651,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="2" width="8.6640625" style="1"/>
+    <col min="2" max="3" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1273,6 +1283,42 @@
       </c>
       <c r="D71" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D72" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D73" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AF081C-5312-46B4-B42B-504B2AF62205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E3223F-385B-4DF0-9805-06B236716295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11520" yWindow="-3864" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23040" yWindow="-3864" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="93">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -324,6 +324,12 @@
   <si>
     <t>Towards active learning: A stopping criterion for the sequential sampling of grain boundary degrees of freedom</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>How to Allocate your Label Budget? Choosing between Active Learning and Learning to Reject in Anomaly Detection</t>
+  </si>
+  <si>
+    <t>ActiveLab: Active Learning with Re-Labeling by Multiple Annotators</t>
   </si>
 </sst>
 </file>
@@ -651,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="8.6640625" style="1"/>
@@ -1321,6 +1327,31 @@
         <v>90</v>
       </c>
     </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D75" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D76" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/posts/readinglist.xlsx
+++ b/posts/readinglist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\other\ia-gu.github.io\posts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E3223F-385B-4DF0-9805-06B236716295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1B9822-3532-495E-9A33-759E9924170C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23040" yWindow="-3864" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13590" yWindow="-738" windowWidth="14400" windowHeight="7362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
   <si>
     <t>A Survey of Deep Active Learning</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>ActiveLab: Active Learning with Re-Labeling by Multiple Annotators</t>
+  </si>
+  <si>
+    <t>Active Learning with Positive and Negative Pairwise Feedback</t>
+  </si>
+  <si>
+    <t>Deep Active Learning in the Presence of Label Noise: A Survey</t>
   </si>
 </sst>
 </file>
@@ -657,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="3" width="8.6640625" style="1"/>
@@ -1352,6 +1358,34 @@
         <v>92</v>
       </c>
     </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2023</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
